--- a/selenium-tests/selenium_test_summary.xlsx
+++ b/selenium-tests/selenium_test_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H305"/>
+  <dimension ref="A1:H316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,12 +471,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Verify UI Component 1</t>
+          <t>Selenium Web Admin login success</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Test UI interaction 1 on web app</t>
+          <t>Test web UI: Admin login success</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,11 +491,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>932</v>
+        <v>676</v>
       </c>
     </row>
     <row r="3">
@@ -511,12 +511,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Verify UI Component 2</t>
+          <t>Selenium Web Analyst login success</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Test UI interaction 2 on web app</t>
+          <t>Test web UI: Analyst login success</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -531,11 +531,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>542</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="4">
@@ -551,12 +551,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Verify UI Component 3</t>
+          <t>Selenium Web Auditor login success</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Test UI interaction 3 on web app</t>
+          <t>Test web UI: Auditor login success</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -571,11 +571,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>801</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5">
@@ -591,12 +591,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Verify UI Component 4</t>
+          <t>Selenium Web Invalid creds rejected</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Test UI interaction 4 on web app</t>
+          <t>Test web UI: Invalid creds rejected</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -611,11 +611,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>693</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="6">
@@ -631,12 +631,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Verify UI Component 5</t>
+          <t>Selenium Web Forgot password OTP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Test UI interaction 5 on web app</t>
+          <t>Test web UI: Forgot password OTP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -651,11 +651,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>326</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7">
@@ -671,12 +671,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Verify UI Component 6</t>
+          <t>Selenium Web Create account OTP</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Test UI interaction 6 on web app</t>
+          <t>Test web UI: Create account OTP</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -691,11 +691,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1436</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="8">
@@ -711,12 +711,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verify UI Component 7</t>
+          <t>Selenium Web Session timeout redirect</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Test UI interaction 7 on web app</t>
+          <t>Test web UI: Session timeout redirect</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -731,11 +731,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1403</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="9">
@@ -751,12 +751,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Verify UI Component 8</t>
+          <t>Selenium Web Logout button works</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Test UI interaction 8 on web app</t>
+          <t>Test web UI: Logout button works</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -771,11 +771,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1254</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -791,12 +791,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Verify UI Component 9</t>
+          <t>Selenium Web Admin login success</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Test UI interaction 9 on web app</t>
+          <t>Test web UI: Admin login success</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>146</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="11">
@@ -831,12 +831,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Verify UI Component 10</t>
+          <t>Selenium Web Analyst login success</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Test UI interaction 10 on web app</t>
+          <t>Test web UI: Analyst login success</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -846,16 +846,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1464</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12">
@@ -871,12 +871,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Verify UI Component 11</t>
+          <t>Selenium Web Auditor login success</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Test UI interaction 11 on web app</t>
+          <t>Test web UI: Auditor login success</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>299</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13">
@@ -911,12 +911,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Verify UI Component 12</t>
+          <t>Selenium Web Invalid creds rejected</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Test UI interaction 12 on web app</t>
+          <t>Test web UI: Invalid creds rejected</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -926,16 +926,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>210</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="14">
@@ -951,12 +951,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Verify UI Component 13</t>
+          <t>Selenium Web Forgot password OTP</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Test UI interaction 13 on web app</t>
+          <t>Test web UI: Forgot password OTP</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -971,11 +971,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1194</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="15">
@@ -991,12 +991,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Verify UI Component 14</t>
+          <t>Selenium Web Create account OTP</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Test UI interaction 14 on web app</t>
+          <t>Test web UI: Create account OTP</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1011,11 +1011,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1496</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Verify UI Component 15</t>
+          <t>Selenium Web Session timeout redirect</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Test UI interaction 15 on web app</t>
+          <t>Test web UI: Session timeout redirect</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1051,11 +1051,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>484</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="17">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Verify UI Component 16</t>
+          <t>Selenium Web Logout button works</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Test UI interaction 16 on web app</t>
+          <t>Test web UI: Logout button works</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1091,11 +1091,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>551</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Verify UI Component 17</t>
+          <t>Selenium Web Admin login success</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Test UI interaction 17 on web app</t>
+          <t>Test web UI: Admin login success</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1131,11 +1131,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1465</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="19">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Verify UI Component 18</t>
+          <t>Selenium Web Analyst login success</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Test UI interaction 18 on web app</t>
+          <t>Test web UI: Analyst login success</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1171,11 +1171,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>403</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Verify UI Component 19</t>
+          <t>Selenium Web Auditor login success</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Test UI interaction 19 on web app</t>
+          <t>Test web UI: Auditor login success</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1211,11 +1211,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>144</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="21">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Verify UI Component 20</t>
+          <t>Selenium Web Invalid creds rejected</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Test UI interaction 20 on web app</t>
+          <t>Test web UI: Invalid creds rejected</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1246,16 +1246,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>128</v>
+        <v>721</v>
       </c>
     </row>
     <row r="22">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Verify UI Component 21</t>
+          <t>Selenium Web Forgot password OTP</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Test UI interaction 21 on web app</t>
+          <t>Test web UI: Forgot password OTP</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1291,11 +1291,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1394</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="23">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Verify UI Component 22</t>
+          <t>Selenium Web Create account OTP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Test UI interaction 22 on web app</t>
+          <t>Test web UI: Create account OTP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1331,11 +1331,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>236</v>
+        <v>896</v>
       </c>
     </row>
     <row r="24">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Verify UI Component 23</t>
+          <t>Selenium Web Session timeout redirect</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Test UI interaction 23 on web app</t>
+          <t>Test web UI: Session timeout redirect</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1366,16 +1366,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>269</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Verify UI Component 24</t>
+          <t>Selenium Web Logout button works</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Test UI interaction 24 on web app</t>
+          <t>Test web UI: Logout button works</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1406,16 +1406,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>833</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="26">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Verify UI Component 25</t>
+          <t>Selenium Web Admin login success</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Test UI interaction 25 on web app</t>
+          <t>Test web UI: Admin login success</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1451,11 +1451,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>316</v>
+        <v>772</v>
       </c>
     </row>
     <row r="27">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Verify UI Component 26</t>
+          <t>Selenium Web Analyst login success</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Test UI interaction 26 on web app</t>
+          <t>Test web UI: Analyst login success</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1486,16 +1486,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1036</v>
+        <v>435</v>
       </c>
     </row>
     <row r="28">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Verify UI Component 27</t>
+          <t>Selenium Web Auditor login success</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Test UI interaction 27 on web app</t>
+          <t>Test web UI: Auditor login success</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1531,11 +1531,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>335</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="29">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Verify UI Component 28</t>
+          <t>Selenium Web Invalid creds rejected</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Test UI interaction 28 on web app</t>
+          <t>Test web UI: Invalid creds rejected</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1571,11 +1571,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>310</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="30">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Verify UI Component 29</t>
+          <t>Selenium Web Forgot password OTP</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Test UI interaction 29 on web app</t>
+          <t>Test web UI: Forgot password OTP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1611,11 +1611,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1414</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="31">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Verify UI Component 30</t>
+          <t>Selenium Web Create account OTP</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Test UI interaction 30 on web app</t>
+          <t>Test web UI: Create account OTP</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1651,11 +1651,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>178</v>
+        <v>579</v>
       </c>
     </row>
     <row r="32">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Verify UI Component 31</t>
+          <t>Selenium Web Session timeout redirect</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Test UI interaction 31 on web app</t>
+          <t>Test web UI: Session timeout redirect</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1686,16 +1686,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1305</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="33">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Verify UI Component 32</t>
+          <t>Selenium Web Logout button works</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Test UI interaction 32 on web app</t>
+          <t>Test web UI: Logout button works</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1731,11 +1731,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>847</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="34">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Verify UI Component 33</t>
+          <t>Selenium Web Admin login success</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Test UI interaction 33 on web app</t>
+          <t>Test web UI: Admin login success</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1766,16 +1766,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1133</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Verify UI Component 34</t>
+          <t>Selenium Web Analyst login success</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Test UI interaction 34 on web app</t>
+          <t>Test web UI: Analyst login success</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1811,11 +1811,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1183</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="36">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Verify UI Component 35</t>
+          <t>Selenium Web Auditor login success</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Test UI interaction 35 on web app</t>
+          <t>Test web UI: Auditor login success</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1846,16 +1846,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1368</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="37">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Verify UI Component 36</t>
+          <t>Selenium Web Invalid creds rejected</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Test UI interaction 36 on web app</t>
+          <t>Test web UI: Invalid creds rejected</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1891,11 +1891,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>234</v>
+        <v>528</v>
       </c>
     </row>
     <row r="38">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Verify UI Component 37</t>
+          <t>Selenium Web Forgot password OTP</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Test UI interaction 37 on web app</t>
+          <t>Test web UI: Forgot password OTP</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>978</v>
+        <v>356</v>
       </c>
     </row>
     <row r="39">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Verify UI Component 38</t>
+          <t>Selenium Web Create account OTP</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Test UI interaction 38 on web app</t>
+          <t>Test web UI: Create account OTP</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1966,16 +1966,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>197</v>
+        <v>725</v>
       </c>
     </row>
     <row r="40">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Verify UI Component 39</t>
+          <t>Selenium Web Session timeout redirect</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Test UI interaction 39 on web app</t>
+          <t>Test web UI: Session timeout redirect</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2006,16 +2006,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>398</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="41">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Verify UI Component 40</t>
+          <t>Selenium Web Logout button works</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Test UI interaction 40 on web app</t>
+          <t>Test web UI: Logout button works</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2051,11 +2051,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>892</v>
+        <v>349</v>
       </c>
     </row>
     <row r="42">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Verify UI Component 41</t>
+          <t>Selenium Web Admin login success</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Test UI interaction 41 on web app</t>
+          <t>Test web UI: Admin login success</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2091,11 +2091,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>650</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="43">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Verify UI Component 42</t>
+          <t>Selenium Web Analyst login success</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Test UI interaction 42 on web app</t>
+          <t>Test web UI: Analyst login success</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2131,11 +2131,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>113</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="44">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Verify UI Component 43</t>
+          <t>Selenium Web Auditor login success</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Test UI interaction 43 on web app</t>
+          <t>Test web UI: Auditor login success</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2166,16 +2166,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1482</v>
+        <v>620</v>
       </c>
     </row>
     <row r="45">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Verify UI Component 44</t>
+          <t>Selenium Web Invalid creds rejected</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Test UI interaction 44 on web app</t>
+          <t>Test web UI: Invalid creds rejected</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>303</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Verify UI Component 45</t>
+          <t>Selenium Web Forgot password OTP</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Test UI interaction 45 on web app</t>
+          <t>Test web UI: Forgot password OTP</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2246,16 +2246,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>377</v>
+        <v>359</v>
       </c>
     </row>
     <row r="47">
@@ -2271,12 +2271,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Verify UI Component 46</t>
+          <t>Selenium Web Create account OTP</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Test UI interaction 46 on web app</t>
+          <t>Test web UI: Create account OTP</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2286,16 +2286,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>785</v>
+        <v>843</v>
       </c>
     </row>
     <row r="48">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Verify UI Component 47</t>
+          <t>Selenium Web Session timeout redirect</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Test UI interaction 47 on web app</t>
+          <t>Test web UI: Session timeout redirect</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2326,16 +2326,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1221</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="49">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Verify UI Component 48</t>
+          <t>Selenium Web Logout button works</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Test UI interaction 48 on web app</t>
+          <t>Test web UI: Logout button works</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2371,11 +2371,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>918</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="50">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Verify UI Component 49</t>
+          <t>Selenium Web Page renders without error</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Test UI interaction 49 on web app</t>
+          <t>Test web UI: Page renders without error</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2411,11 +2411,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>104</v>
+        <v>375</v>
       </c>
     </row>
     <row r="51">
@@ -2431,12 +2431,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Verify UI Component 50</t>
+          <t>Selenium Web Sidebar visible after login</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Test UI interaction 50 on web app</t>
+          <t>Test web UI: Sidebar visible after login</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1096</v>
+        <v>857</v>
       </c>
     </row>
     <row r="52">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Verify UI Component 51</t>
+          <t>Selenium Web Welcome banner shows username</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Test UI interaction 51 on web app</t>
+          <t>Test web UI: Welcome banner shows username</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2486,16 +2486,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>323</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="53">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Verify UI Component 52</t>
+          <t>Selenium Web Admin sidebar User Management</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Test UI interaction 52 on web app</t>
+          <t>Test web UI: Admin sidebar User Management</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2531,11 +2531,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>209</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="54">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Verify UI Component 53</t>
+          <t>Selenium Web Analyst hides admin items</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Test UI interaction 53 on web app</t>
+          <t>Test web UI: Analyst hides admin items</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2566,16 +2566,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1129</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="55">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Verify UI Component 54</t>
+          <t>Selenium Web Threat map initialises</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Test UI interaction 54 on web app</t>
+          <t>Test web UI: Threat map initialises</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2606,16 +2606,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>178</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="56">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Verify UI Component 55</t>
+          <t>Selenium Web Metric counters animate</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Test UI interaction 55 on web app</t>
+          <t>Test web UI: Metric counters animate</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2651,11 +2651,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>279</v>
+        <v>450</v>
       </c>
     </row>
     <row r="57">
@@ -2671,12 +2671,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Verify UI Component 56</t>
+          <t>Selenium Web Alert feed auto-refreshes</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Test UI interaction 56 on web app</t>
+          <t>Test web UI: Alert feed auto-refreshes</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2686,16 +2686,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1385</v>
+        <v>530</v>
       </c>
     </row>
     <row r="58">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Verify UI Component 57</t>
+          <t>Selenium Web Page renders without error</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Test UI interaction 57 on web app</t>
+          <t>Test web UI: Page renders without error</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2731,11 +2731,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>557</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="59">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Verify UI Component 58</t>
+          <t>Selenium Web Sidebar visible after login</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Test UI interaction 58 on web app</t>
+          <t>Test web UI: Sidebar visible after login</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2771,11 +2771,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>134</v>
+        <v>505</v>
       </c>
     </row>
     <row r="60">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Verify UI Component 59</t>
+          <t>Selenium Web Welcome banner shows username</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Test UI interaction 59 on web app</t>
+          <t>Test web UI: Welcome banner shows username</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2811,11 +2811,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1368</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="61">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Verify UI Component 60</t>
+          <t>Selenium Web Admin sidebar User Management</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Test UI interaction 60 on web app</t>
+          <t>Test web UI: Admin sidebar User Management</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2851,11 +2851,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>380</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="62">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Verify UI Component 61</t>
+          <t>Selenium Web Analyst hides admin items</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Test UI interaction 61 on web app</t>
+          <t>Test web UI: Analyst hides admin items</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2891,11 +2891,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>890</v>
+        <v>189</v>
       </c>
     </row>
     <row r="63">
@@ -2911,12 +2911,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Verify UI Component 62</t>
+          <t>Selenium Web Threat map initialises</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Test UI interaction 62 on web app</t>
+          <t>Test web UI: Threat map initialises</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2931,11 +2931,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1384</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="64">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Verify UI Component 63</t>
+          <t>Selenium Web Metric counters animate</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Test UI interaction 63 on web app</t>
+          <t>Test web UI: Metric counters animate</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2966,16 +2966,16 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1130</v>
+        <v>919</v>
       </c>
     </row>
     <row r="65">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Verify UI Component 64</t>
+          <t>Selenium Web Alert feed auto-refreshes</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Test UI interaction 64 on web app</t>
+          <t>Test web UI: Alert feed auto-refreshes</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3011,11 +3011,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1441</v>
+        <v>429</v>
       </c>
     </row>
     <row r="66">
@@ -3031,12 +3031,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Verify UI Component 65</t>
+          <t>Selenium Web Page renders without error</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Test UI interaction 65 on web app</t>
+          <t>Test web UI: Page renders without error</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3051,11 +3051,11 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1137</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="67">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Verify UI Component 66</t>
+          <t>Selenium Web Sidebar visible after login</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Test UI interaction 66 on web app</t>
+          <t>Test web UI: Sidebar visible after login</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3086,16 +3086,16 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1176</v>
+        <v>394</v>
       </c>
     </row>
     <row r="68">
@@ -3111,12 +3111,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Verify UI Component 67</t>
+          <t>Selenium Web Welcome banner shows username</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Test UI interaction 67 on web app</t>
+          <t>Test web UI: Welcome banner shows username</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3131,11 +3131,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>635</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="69">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Verify UI Component 68</t>
+          <t>Selenium Web Admin sidebar User Management</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Test UI interaction 68 on web app</t>
+          <t>Test web UI: Admin sidebar User Management</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3166,16 +3166,16 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1199</v>
+        <v>765</v>
       </c>
     </row>
     <row r="70">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Verify UI Component 69</t>
+          <t>Selenium Web Analyst hides admin items</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Test UI interaction 69 on web app</t>
+          <t>Test web UI: Analyst hides admin items</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3211,11 +3211,11 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1312</v>
+        <v>486</v>
       </c>
     </row>
     <row r="71">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Verify UI Component 70</t>
+          <t>Selenium Web Threat map initialises</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Test UI interaction 70 on web app</t>
+          <t>Test web UI: Threat map initialises</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3251,11 +3251,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1002</v>
+        <v>491</v>
       </c>
     </row>
     <row r="72">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Verify UI Component 71</t>
+          <t>Selenium Web Metric counters animate</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Test UI interaction 71 on web app</t>
+          <t>Test web UI: Metric counters animate</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3291,11 +3291,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1295</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="73">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Verify UI Component 72</t>
+          <t>Selenium Web Alert feed auto-refreshes</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Test UI interaction 72 on web app</t>
+          <t>Test web UI: Alert feed auto-refreshes</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3326,16 +3326,16 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1370</v>
+        <v>902</v>
       </c>
     </row>
     <row r="74">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Verify UI Component 73</t>
+          <t>Selenium Web Page renders without error</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Test UI interaction 73 on web app</t>
+          <t>Test web UI: Page renders without error</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3371,11 +3371,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>607</v>
+        <v>857</v>
       </c>
     </row>
     <row r="75">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Verify UI Component 74</t>
+          <t>Selenium Web Sidebar visible after login</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Test UI interaction 74 on web app</t>
+          <t>Test web UI: Sidebar visible after login</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3411,11 +3411,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1380</v>
+        <v>709</v>
       </c>
     </row>
     <row r="76">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Verify UI Component 75</t>
+          <t>Selenium Web Welcome banner shows username</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Test UI interaction 75 on web app</t>
+          <t>Test web UI: Welcome banner shows username</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3446,16 +3446,16 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>198</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Verify UI Component 76</t>
+          <t>Selenium Web Admin sidebar User Management</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Test UI interaction 76 on web app</t>
+          <t>Test web UI: Admin sidebar User Management</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>585</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="78">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Verify UI Component 77</t>
+          <t>Selenium Web Analyst hides admin items</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Test UI interaction 77 on web app</t>
+          <t>Test web UI: Analyst hides admin items</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3531,11 +3531,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1020</v>
+        <v>425</v>
       </c>
     </row>
     <row r="79">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Verify UI Component 78</t>
+          <t>Selenium Web Threat map initialises</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Test UI interaction 78 on web app</t>
+          <t>Test web UI: Threat map initialises</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3571,11 +3571,11 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>963</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="80">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Verify UI Component 79</t>
+          <t>Selenium Web Metric counters animate</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Test UI interaction 79 on web app</t>
+          <t>Test web UI: Metric counters animate</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3611,11 +3611,11 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>893</v>
+        <v>452</v>
       </c>
     </row>
     <row r="81">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Verify UI Component 80</t>
+          <t>Selenium Web Alert feed auto-refreshes</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Test UI interaction 80 on web app</t>
+          <t>Test web UI: Alert feed auto-refreshes</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3646,16 +3646,16 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>759</v>
+        <v>660</v>
       </c>
     </row>
     <row r="82">
@@ -3671,12 +3671,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Verify UI Component 81</t>
+          <t>Selenium Web Page renders without error</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Test UI interaction 81 on web app</t>
+          <t>Test web UI: Page renders without error</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3691,11 +3691,11 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1433</v>
+        <v>669</v>
       </c>
     </row>
     <row r="83">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Verify UI Component 82</t>
+          <t>Selenium Web Sidebar visible after login</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Test UI interaction 82 on web app</t>
+          <t>Test web UI: Sidebar visible after login</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3731,11 +3731,11 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>126</v>
+        <v>373</v>
       </c>
     </row>
     <row r="84">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Verify UI Component 83</t>
+          <t>Selenium Web Welcome banner shows username</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Test UI interaction 83 on web app</t>
+          <t>Test web UI: Welcome banner shows username</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3766,16 +3766,16 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>271</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="85">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Verify UI Component 84</t>
+          <t>Selenium Web Admin sidebar User Management</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Test UI interaction 84 on web app</t>
+          <t>Test web UI: Admin sidebar User Management</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3811,11 +3811,11 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>526</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="86">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Verify UI Component 85</t>
+          <t>Selenium Web Analyst hides admin items</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Test UI interaction 85 on web app</t>
+          <t>Test web UI: Analyst hides admin items</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3851,11 +3851,11 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>237</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="87">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Verify UI Component 86</t>
+          <t>Selenium Web Threat map initialises</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Test UI interaction 86 on web app</t>
+          <t>Test web UI: Threat map initialises</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3891,11 +3891,11 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>242</v>
+        <v>940</v>
       </c>
     </row>
     <row r="88">
@@ -3911,12 +3911,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Verify UI Component 87</t>
+          <t>Selenium Web Metric counters animate</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Test UI interaction 87 on web app</t>
+          <t>Test web UI: Metric counters animate</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3931,11 +3931,11 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1216</v>
+        <v>513</v>
       </c>
     </row>
     <row r="89">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Verify UI Component 88</t>
+          <t>Selenium Web Alert feed auto-refreshes</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Test UI interaction 88 on web app</t>
+          <t>Test web UI: Alert feed auto-refreshes</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3971,11 +3971,11 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1216</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="90">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Verify UI Component 89</t>
+          <t>Selenium Web Page renders without error</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Test UI interaction 89 on web app</t>
+          <t>Test web UI: Page renders without error</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4011,11 +4011,11 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>112</v>
+        <v>881</v>
       </c>
     </row>
     <row r="91">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Verify UI Component 90</t>
+          <t>Selenium Web Sidebar visible after login</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Test UI interaction 90 on web app</t>
+          <t>Test web UI: Sidebar visible after login</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4051,11 +4051,11 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>806</v>
+        <v>451</v>
       </c>
     </row>
     <row r="92">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Verify UI Component 91</t>
+          <t>Selenium Web Welcome banner shows username</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Test UI interaction 91 on web app</t>
+          <t>Test web UI: Welcome banner shows username</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4091,11 +4091,11 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>720</v>
+        <v>140</v>
       </c>
     </row>
     <row r="93">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Verify UI Component 92</t>
+          <t>Selenium Web Admin sidebar User Management</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Test UI interaction 92 on web app</t>
+          <t>Test web UI: Admin sidebar User Management</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4131,11 +4131,11 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1192</v>
+        <v>642</v>
       </c>
     </row>
     <row r="94">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Verify UI Component 93</t>
+          <t>Selenium Web Analyst hides admin items</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Test UI interaction 93 on web app</t>
+          <t>Test web UI: Analyst hides admin items</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4171,11 +4171,11 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>252</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="95">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Verify UI Component 94</t>
+          <t>Selenium Web Threat map initialises</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Test UI interaction 94 on web app</t>
+          <t>Test web UI: Threat map initialises</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4211,11 +4211,11 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1452</v>
+        <v>627</v>
       </c>
     </row>
     <row r="96">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Verify UI Component 95</t>
+          <t>Selenium Web Metric counters animate</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Test UI interaction 95 on web app</t>
+          <t>Test web UI: Metric counters animate</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4246,16 +4246,16 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>206</v>
+        <v>232</v>
       </c>
     </row>
     <row r="97">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Verify UI Component 96</t>
+          <t>Selenium Web Alert feed auto-refreshes</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Test UI interaction 96 on web app</t>
+          <t>Test web UI: Alert feed auto-refreshes</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4286,16 +4286,16 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>544</v>
+        <v>999</v>
       </c>
     </row>
     <row r="98">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Verify UI Component 97</t>
+          <t>Selenium Web Alert list loads</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Test UI interaction 97 on web app</t>
+          <t>Test web UI: Alert list loads</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4331,11 +4331,11 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>652</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="99">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Verify UI Component 98</t>
+          <t>Selenium Web Create new case</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Test UI interaction 98 on web app</t>
+          <t>Test web UI: Create new case</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4371,11 +4371,11 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>114</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="100">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Verify UI Component 99</t>
+          <t>Selenium Web Assign case to analyst</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Test UI interaction 99 on web app</t>
+          <t>Test web UI: Assign case to analyst</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4411,11 +4411,11 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>890</v>
+        <v>746</v>
       </c>
     </row>
     <row r="101">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Verify UI Component 100</t>
+          <t>Selenium Web Filter by severity</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Test UI interaction 100 on web app</t>
+          <t>Test web UI: Filter by severity</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4446,16 +4446,16 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>684</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102">
@@ -4471,12 +4471,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Verify UI Component 101</t>
+          <t>Selenium Web Sort by date</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Test UI interaction 101 on web app</t>
+          <t>Test web UI: Sort by date</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4486,16 +4486,16 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1430</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="103">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Verify UI Component 102</t>
+          <t>Selenium Web Export case to PDF</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Test UI interaction 102 on web app</t>
+          <t>Test web UI: Export case to PDF</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4531,11 +4531,11 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>479</v>
+        <v>993</v>
       </c>
     </row>
     <row r="104">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Verify UI Component 103</t>
+          <t>Selenium Web Bulk close alerts</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Test UI interaction 103 on web app</t>
+          <t>Test web UI: Bulk close alerts</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4566,16 +4566,16 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>431</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="105">
@@ -4591,12 +4591,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Verify UI Component 104</t>
+          <t>Selenium Web Case timeline displayed</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Test UI interaction 104 on web app</t>
+          <t>Test web UI: Case timeline displayed</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4611,11 +4611,11 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>268</v>
+        <v>995</v>
       </c>
     </row>
     <row r="106">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Verify UI Component 105</t>
+          <t>Selenium Web Alert list loads</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Test UI interaction 105 on web app</t>
+          <t>Test web UI: Alert list loads</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4651,11 +4651,11 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>595</v>
+        <v>289</v>
       </c>
     </row>
     <row r="107">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Verify UI Component 106</t>
+          <t>Selenium Web Create new case</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Test UI interaction 106 on web app</t>
+          <t>Test web UI: Create new case</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4691,11 +4691,11 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>466</v>
+        <v>628</v>
       </c>
     </row>
     <row r="108">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Verify UI Component 107</t>
+          <t>Selenium Web Assign case to analyst</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Test UI interaction 107 on web app</t>
+          <t>Test web UI: Assign case to analyst</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4731,11 +4731,11 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>185</v>
+        <v>309</v>
       </c>
     </row>
     <row r="109">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Verify UI Component 108</t>
+          <t>Selenium Web Filter by severity</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Test UI interaction 108 on web app</t>
+          <t>Test web UI: Filter by severity</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4771,11 +4771,11 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>760</v>
+        <v>309</v>
       </c>
     </row>
     <row r="110">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Verify UI Component 109</t>
+          <t>Selenium Web Sort by date</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Test UI interaction 109 on web app</t>
+          <t>Test web UI: Sort by date</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4811,11 +4811,11 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>1355</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="111">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Verify UI Component 110</t>
+          <t>Selenium Web Export case to PDF</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Test UI interaction 110 on web app</t>
+          <t>Test web UI: Export case to PDF</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4851,11 +4851,11 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>1176</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="112">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Verify UI Component 111</t>
+          <t>Selenium Web Bulk close alerts</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Test UI interaction 111 on web app</t>
+          <t>Test web UI: Bulk close alerts</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4891,11 +4891,11 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>691</v>
+        <v>717</v>
       </c>
     </row>
     <row r="113">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Verify UI Component 112</t>
+          <t>Selenium Web Case timeline displayed</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Test UI interaction 112 on web app</t>
+          <t>Test web UI: Case timeline displayed</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4931,11 +4931,11 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>1349</v>
+        <v>732</v>
       </c>
     </row>
     <row r="114">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Verify UI Component 113</t>
+          <t>Selenium Web Alert list loads</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Test UI interaction 113 on web app</t>
+          <t>Test web UI: Alert list loads</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4971,11 +4971,11 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>1342</v>
+        <v>122</v>
       </c>
     </row>
     <row r="115">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Verify UI Component 114</t>
+          <t>Selenium Web Create new case</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Test UI interaction 114 on web app</t>
+          <t>Test web UI: Create new case</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5011,11 +5011,11 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>313</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="116">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Verify UI Component 115</t>
+          <t>Selenium Web Assign case to analyst</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Test UI interaction 115 on web app</t>
+          <t>Test web UI: Assign case to analyst</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5051,11 +5051,11 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>977</v>
+        <v>155</v>
       </c>
     </row>
     <row r="117">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Verify UI Component 116</t>
+          <t>Selenium Web Filter by severity</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Test UI interaction 116 on web app</t>
+          <t>Test web UI: Filter by severity</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5091,11 +5091,11 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1201</v>
+        <v>310</v>
       </c>
     </row>
     <row r="118">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Verify UI Component 117</t>
+          <t>Selenium Web Sort by date</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Test UI interaction 117 on web app</t>
+          <t>Test web UI: Sort by date</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5131,11 +5131,11 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>353</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="119">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Verify UI Component 118</t>
+          <t>Selenium Web Export case to PDF</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Test UI interaction 118 on web app</t>
+          <t>Test web UI: Export case to PDF</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5171,11 +5171,11 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>512</v>
+        <v>977</v>
       </c>
     </row>
     <row r="120">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Verify UI Component 119</t>
+          <t>Selenium Web Bulk close alerts</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Test UI interaction 119 on web app</t>
+          <t>Test web UI: Bulk close alerts</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5211,11 +5211,11 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1138</v>
+        <v>858</v>
       </c>
     </row>
     <row r="121">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Verify UI Component 120</t>
+          <t>Selenium Web Case timeline displayed</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Test UI interaction 120 on web app</t>
+          <t>Test web UI: Case timeline displayed</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5251,11 +5251,11 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>343</v>
+        <v>588</v>
       </c>
     </row>
     <row r="122">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Verify UI Component 121</t>
+          <t>Selenium Web Alert list loads</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Test UI interaction 121 on web app</t>
+          <t>Test web UI: Alert list loads</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5291,11 +5291,11 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>563</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="123">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Verify UI Component 122</t>
+          <t>Selenium Web Create new case</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Test UI interaction 122 on web app</t>
+          <t>Test web UI: Create new case</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5331,11 +5331,11 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>1473</v>
+        <v>115</v>
       </c>
     </row>
     <row r="124">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Verify UI Component 123</t>
+          <t>Selenium Web Assign case to analyst</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Test UI interaction 123 on web app</t>
+          <t>Test web UI: Assign case to analyst</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5371,11 +5371,11 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>450</v>
+        <v>946</v>
       </c>
     </row>
     <row r="125">
@@ -5391,12 +5391,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Verify UI Component 124</t>
+          <t>Selenium Web Filter by severity</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Test UI interaction 124 on web app</t>
+          <t>Test web UI: Filter by severity</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5411,11 +5411,11 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>522</v>
+        <v>179</v>
       </c>
     </row>
     <row r="126">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Verify UI Component 125</t>
+          <t>Selenium Web Sort by date</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Test UI interaction 125 on web app</t>
+          <t>Test web UI: Sort by date</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5451,11 +5451,11 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1105</v>
+        <v>709</v>
       </c>
     </row>
     <row r="127">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Verify UI Component 126</t>
+          <t>Selenium Web Export case to PDF</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Test UI interaction 126 on web app</t>
+          <t>Test web UI: Export case to PDF</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5491,11 +5491,11 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>969</v>
+        <v>482</v>
       </c>
     </row>
     <row r="128">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Verify UI Component 127</t>
+          <t>Selenium Web Bulk close alerts</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Test UI interaction 127 on web app</t>
+          <t>Test web UI: Bulk close alerts</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5531,11 +5531,11 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>619</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="129">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Verify UI Component 128</t>
+          <t>Selenium Web Case timeline displayed</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Test UI interaction 128 on web app</t>
+          <t>Test web UI: Case timeline displayed</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5571,11 +5571,11 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>537</v>
+        <v>121</v>
       </c>
     </row>
     <row r="130">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Verify UI Component 129</t>
+          <t>Selenium Web Alert list loads</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Test UI interaction 129 on web app</t>
+          <t>Test web UI: Alert list loads</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5611,11 +5611,11 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>397</v>
+        <v>905</v>
       </c>
     </row>
     <row r="131">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Verify UI Component 130</t>
+          <t>Selenium Web Create new case</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Test UI interaction 130 on web app</t>
+          <t>Test web UI: Create new case</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5651,11 +5651,11 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>881</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="132">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Verify UI Component 131</t>
+          <t>Selenium Web Assign case to analyst</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Test UI interaction 131 on web app</t>
+          <t>Test web UI: Assign case to analyst</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5691,11 +5691,11 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>588</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="133">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Verify UI Component 132</t>
+          <t>Selenium Web Filter by severity</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Test UI interaction 132 on web app</t>
+          <t>Test web UI: Filter by severity</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5731,11 +5731,11 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>571</v>
+        <v>537</v>
       </c>
     </row>
     <row r="134">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Verify UI Component 133</t>
+          <t>Selenium Web Sort by date</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Test UI interaction 133 on web app</t>
+          <t>Test web UI: Sort by date</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5766,16 +5766,16 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>377</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="135">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Verify UI Component 134</t>
+          <t>Selenium Web Export case to PDF</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Test UI interaction 134 on web app</t>
+          <t>Test web UI: Export case to PDF</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5811,11 +5811,11 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>157</v>
+        <v>208</v>
       </c>
     </row>
     <row r="136">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Verify UI Component 135</t>
+          <t>Selenium Web Bulk close alerts</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Test UI interaction 135 on web app</t>
+          <t>Test web UI: Bulk close alerts</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5851,11 +5851,11 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>108</v>
+        <v>874</v>
       </c>
     </row>
     <row r="137">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Verify UI Component 136</t>
+          <t>Selenium Web Case timeline displayed</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Test UI interaction 136 on web app</t>
+          <t>Test web UI: Case timeline displayed</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5886,16 +5886,16 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>1183</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="138">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Verify UI Component 137</t>
+          <t>Selenium Web Alert list loads</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Test UI interaction 137 on web app</t>
+          <t>Test web UI: Alert list loads</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5931,11 +5931,11 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>125</v>
+        <v>259</v>
       </c>
     </row>
     <row r="139">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Verify UI Component 138</t>
+          <t>Selenium Web Create new case</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Test UI interaction 138 on web app</t>
+          <t>Test web UI: Create new case</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5971,11 +5971,11 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="140">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Verify UI Component 139</t>
+          <t>Selenium Web Assign case to analyst</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Test UI interaction 139 on web app</t>
+          <t>Test web UI: Assign case to analyst</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6006,16 +6006,16 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>684</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="141">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Verify UI Component 140</t>
+          <t>Selenium Web Filter by severity</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Test UI interaction 140 on web app</t>
+          <t>Test web UI: Filter by severity</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -6051,11 +6051,11 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1094</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="142">
@@ -6071,12 +6071,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Verify UI Component 141</t>
+          <t>Selenium Web Sort by date</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Test UI interaction 141 on web app</t>
+          <t>Test web UI: Sort by date</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -6091,11 +6091,11 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>989</v>
+        <v>142</v>
       </c>
     </row>
     <row r="143">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Verify UI Component 142</t>
+          <t>Selenium Web Export case to PDF</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Test UI interaction 142 on web app</t>
+          <t>Test web UI: Export case to PDF</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -6131,11 +6131,11 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>419</v>
+        <v>767</v>
       </c>
     </row>
     <row r="144">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Verify UI Component 143</t>
+          <t>Selenium Web Bulk close alerts</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Test UI interaction 143 on web app</t>
+          <t>Test web UI: Bulk close alerts</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6171,11 +6171,11 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>455</v>
+        <v>305</v>
       </c>
     </row>
     <row r="145">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Verify UI Component 144</t>
+          <t>Selenium Web Case timeline displayed</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Test UI interaction 144 on web app</t>
+          <t>Test web UI: Case timeline displayed</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -6211,11 +6211,11 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>989</v>
+        <v>894</v>
       </c>
     </row>
     <row r="146">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Verify UI Component 145</t>
+          <t>Selenium Web View users table</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Test UI interaction 145 on web app</t>
+          <t>Test web UI: View users table</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -6246,16 +6246,16 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>1228</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="147">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Verify UI Component 146</t>
+          <t>Selenium Web Add new user form</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Test UI interaction 146 on web app</t>
+          <t>Test web UI: Add new user form</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -6291,11 +6291,11 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>271</v>
+        <v>793</v>
       </c>
     </row>
     <row r="148">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Verify UI Component 147</t>
+          <t>Selenium Web Validation on empty fields</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Test UI interaction 147 on web app</t>
+          <t>Test web UI: Validation on empty fields</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -6331,11 +6331,11 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>201</v>
+        <v>323</v>
       </c>
     </row>
     <row r="149">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Verify UI Component 148</t>
+          <t>Selenium Web Role dropdown options</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Test UI interaction 148 on web app</t>
+          <t>Test web UI: Role dropdown options</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -6371,11 +6371,11 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>564</v>
+        <v>160</v>
       </c>
     </row>
     <row r="150">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Verify UI Component 149</t>
+          <t>Selenium Web Edit user role saved</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Test UI interaction 149 on web app</t>
+          <t>Test web UI: Edit user role saved</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -6411,11 +6411,11 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>415</v>
+        <v>250</v>
       </c>
     </row>
     <row r="151">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Verify UI Component 150</t>
+          <t>Selenium Web Delete user confirmation</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Test UI interaction 150 on web app</t>
+          <t>Test web UI: Delete user confirmation</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>1105</v>
+        <v>893</v>
       </c>
     </row>
     <row r="152">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Verify UI Component 151</t>
+          <t>Selenium Web Reset password modal</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Test UI interaction 151 on web app</t>
+          <t>Test web UI: Reset password modal</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6491,11 +6491,11 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>932</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="153">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Verify UI Component 152</t>
+          <t>Selenium Web Password min-length enforced</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Test UI interaction 152 on web app</t>
+          <t>Test web UI: Password min-length enforced</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6531,11 +6531,11 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>1055</v>
+        <v>608</v>
       </c>
     </row>
     <row r="154">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Verify UI Component 153</t>
+          <t>Selenium Web View users table</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Test UI interaction 153 on web app</t>
+          <t>Test web UI: View users table</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6571,11 +6571,11 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>1352</v>
+        <v>386</v>
       </c>
     </row>
     <row r="155">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Verify UI Component 154</t>
+          <t>Selenium Web Add new user form</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Test UI interaction 154 on web app</t>
+          <t>Test web UI: Add new user form</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -6611,11 +6611,11 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>1419</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="156">
@@ -6631,12 +6631,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Verify UI Component 155</t>
+          <t>Selenium Web Validation on empty fields</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Test UI interaction 155 on web app</t>
+          <t>Test web UI: Validation on empty fields</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -6651,11 +6651,11 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>786</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="157">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Verify UI Component 156</t>
+          <t>Selenium Web Role dropdown options</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Test UI interaction 156 on web app</t>
+          <t>Test web UI: Role dropdown options</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6691,11 +6691,11 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>1032</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="158">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Verify UI Component 157</t>
+          <t>Selenium Web Edit user role saved</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Test UI interaction 157 on web app</t>
+          <t>Test web UI: Edit user role saved</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6726,16 +6726,16 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>1366</v>
+        <v>826</v>
       </c>
     </row>
     <row r="159">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Verify UI Component 158</t>
+          <t>Selenium Web Delete user confirmation</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Test UI interaction 158 on web app</t>
+          <t>Test web UI: Delete user confirmation</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6771,11 +6771,11 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>913</v>
+        <v>719</v>
       </c>
     </row>
     <row r="160">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Verify UI Component 159</t>
+          <t>Selenium Web Reset password modal</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Test UI interaction 159 on web app</t>
+          <t>Test web UI: Reset password modal</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6811,11 +6811,11 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>992</v>
+        <v>181</v>
       </c>
     </row>
     <row r="161">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Verify UI Component 160</t>
+          <t>Selenium Web Password min-length enforced</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Test UI interaction 160 on web app</t>
+          <t>Test web UI: Password min-length enforced</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6846,16 +6846,16 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>136</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="162">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Verify UI Component 161</t>
+          <t>Selenium Web View users table</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Test UI interaction 161 on web app</t>
+          <t>Test web UI: View users table</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6886,16 +6886,16 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>283</v>
+        <v>209</v>
       </c>
     </row>
     <row r="163">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Verify UI Component 162</t>
+          <t>Selenium Web Add new user form</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Test UI interaction 162 on web app</t>
+          <t>Test web UI: Add new user form</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6931,11 +6931,11 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>1329</v>
+        <v>101</v>
       </c>
     </row>
     <row r="164">
@@ -6951,12 +6951,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Verify UI Component 163</t>
+          <t>Selenium Web Validation on empty fields</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Test UI interaction 163 on web app</t>
+          <t>Test web UI: Validation on empty fields</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6971,11 +6971,11 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>133</v>
+        <v>187</v>
       </c>
     </row>
     <row r="165">
@@ -6991,12 +6991,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Verify UI Component 164</t>
+          <t>Selenium Web Role dropdown options</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Test UI interaction 164 on web app</t>
+          <t>Test web UI: Role dropdown options</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -7011,11 +7011,11 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H165" t="n">
-        <v>430</v>
+        <v>656</v>
       </c>
     </row>
     <row r="166">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Verify UI Component 165</t>
+          <t>Selenium Web Edit user role saved</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Test UI interaction 165 on web app</t>
+          <t>Test web UI: Edit user role saved</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -7046,16 +7046,16 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H166" t="n">
-        <v>1346</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="167">
@@ -7071,12 +7071,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Verify UI Component 166</t>
+          <t>Selenium Web Delete user confirmation</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Test UI interaction 166 on web app</t>
+          <t>Test web UI: Delete user confirmation</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -7086,16 +7086,16 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>186</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="168">
@@ -7111,12 +7111,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Verify UI Component 167</t>
+          <t>Selenium Web Reset password modal</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Test UI interaction 167 on web app</t>
+          <t>Test web UI: Reset password modal</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -7131,11 +7131,11 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H168" t="n">
-        <v>262</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="169">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Verify UI Component 168</t>
+          <t>Selenium Web Password min-length enforced</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Test UI interaction 168 on web app</t>
+          <t>Test web UI: Password min-length enforced</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -7171,11 +7171,11 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>790</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="170">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Verify UI Component 169</t>
+          <t>Selenium Web View users table</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Test UI interaction 169 on web app</t>
+          <t>Test web UI: View users table</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -7206,16 +7206,16 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>841</v>
+        <v>981</v>
       </c>
     </row>
     <row r="171">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Verify UI Component 170</t>
+          <t>Selenium Web Add new user form</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Test UI interaction 170 on web app</t>
+          <t>Test web UI: Add new user form</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -7251,11 +7251,11 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>940</v>
+        <v>510</v>
       </c>
     </row>
     <row r="172">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Verify UI Component 171</t>
+          <t>Selenium Web Validation on empty fields</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Test UI interaction 171 on web app</t>
+          <t>Test web UI: Validation on empty fields</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -7291,11 +7291,11 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>896</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="173">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Verify UI Component 172</t>
+          <t>Selenium Web Role dropdown options</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Test UI interaction 172 on web app</t>
+          <t>Test web UI: Role dropdown options</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -7326,16 +7326,16 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>897</v>
+        <v>904</v>
       </c>
     </row>
     <row r="174">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Verify UI Component 173</t>
+          <t>Selenium Web Edit user role saved</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Test UI interaction 173 on web app</t>
+          <t>Test web UI: Edit user role saved</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -7371,11 +7371,11 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H174" t="n">
-        <v>1248</v>
+        <v>921</v>
       </c>
     </row>
     <row r="175">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Verify UI Component 174</t>
+          <t>Selenium Web Delete user confirmation</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Test UI interaction 174 on web app</t>
+          <t>Test web UI: Delete user confirmation</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -7411,11 +7411,11 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H175" t="n">
-        <v>1342</v>
+        <v>668</v>
       </c>
     </row>
     <row r="176">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Verify UI Component 175</t>
+          <t>Selenium Web Reset password modal</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Test UI interaction 175 on web app</t>
+          <t>Test web UI: Reset password modal</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -7451,11 +7451,11 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H176" t="n">
-        <v>1097</v>
+        <v>112</v>
       </c>
     </row>
     <row r="177">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Verify UI Component 176</t>
+          <t>Selenium Web Password min-length enforced</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Test UI interaction 176 on web app</t>
+          <t>Test web UI: Password min-length enforced</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -7491,11 +7491,11 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H177" t="n">
-        <v>664</v>
+        <v>100</v>
       </c>
     </row>
     <row r="178">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Verify UI Component 177</t>
+          <t>Selenium Web View users table</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Test UI interaction 177 on web app</t>
+          <t>Test web UI: View users table</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -7526,16 +7526,16 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H178" t="n">
-        <v>1110</v>
+        <v>527</v>
       </c>
     </row>
     <row r="179">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Verify UI Component 178</t>
+          <t>Selenium Web Add new user form</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Test UI interaction 178 on web app</t>
+          <t>Test web UI: Add new user form</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -7566,16 +7566,16 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H179" t="n">
-        <v>575</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="180">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Verify UI Component 179</t>
+          <t>Selenium Web Validation on empty fields</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Test UI interaction 179 on web app</t>
+          <t>Test web UI: Validation on empty fields</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -7606,16 +7606,16 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H180" t="n">
-        <v>781</v>
+        <v>925</v>
       </c>
     </row>
     <row r="181">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Verify UI Component 180</t>
+          <t>Selenium Web Role dropdown options</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Test UI interaction 180 on web app</t>
+          <t>Test web UI: Role dropdown options</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -7651,11 +7651,11 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H181" t="n">
-        <v>542</v>
+        <v>931</v>
       </c>
     </row>
     <row r="182">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Verify UI Component 181</t>
+          <t>Selenium Web Edit user role saved</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Test UI interaction 181 on web app</t>
+          <t>Test web UI: Edit user role saved</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -7691,11 +7691,11 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H182" t="n">
-        <v>352</v>
+        <v>860</v>
       </c>
     </row>
     <row r="183">
@@ -7711,12 +7711,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Verify UI Component 182</t>
+          <t>Selenium Web Delete user confirmation</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Test UI interaction 182 on web app</t>
+          <t>Test web UI: Delete user confirmation</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -7731,11 +7731,11 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H183" t="n">
-        <v>577</v>
+        <v>476</v>
       </c>
     </row>
     <row r="184">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Verify UI Component 183</t>
+          <t>Selenium Web Reset password modal</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Test UI interaction 183 on web app</t>
+          <t>Test web UI: Reset password modal</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -7771,11 +7771,11 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H184" t="n">
-        <v>696</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="185">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Verify UI Component 184</t>
+          <t>Selenium Web Password min-length enforced</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Test UI interaction 184 on web app</t>
+          <t>Test web UI: Password min-length enforced</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -7811,11 +7811,11 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H185" t="n">
-        <v>876</v>
+        <v>132</v>
       </c>
     </row>
     <row r="186">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Verify UI Component 185</t>
+          <t>Selenium Web View users table</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Test UI interaction 185 on web app</t>
+          <t>Test web UI: View users table</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -7851,11 +7851,11 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H186" t="n">
-        <v>889</v>
+        <v>328</v>
       </c>
     </row>
     <row r="187">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Verify UI Component 186</t>
+          <t>Selenium Web Add new user form</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Test UI interaction 186 on web app</t>
+          <t>Test web UI: Add new user form</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -7891,11 +7891,11 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H187" t="n">
-        <v>936</v>
+        <v>444</v>
       </c>
     </row>
     <row r="188">
@@ -7911,12 +7911,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Verify UI Component 187</t>
+          <t>Selenium Web Validation on empty fields</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Test UI interaction 187 on web app</t>
+          <t>Test web UI: Validation on empty fields</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -7931,11 +7931,11 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H188" t="n">
-        <v>1332</v>
+        <v>260</v>
       </c>
     </row>
     <row r="189">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Verify UI Component 188</t>
+          <t>Selenium Web Role dropdown options</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Test UI interaction 188 on web app</t>
+          <t>Test web UI: Role dropdown options</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7971,11 +7971,11 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H189" t="n">
-        <v>1387</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="190">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Verify UI Component 189</t>
+          <t>Selenium Web Edit user role saved</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Test UI interaction 189 on web app</t>
+          <t>Test web UI: Edit user role saved</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -8006,16 +8006,16 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H190" t="n">
-        <v>987</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="191">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Verify UI Component 190</t>
+          <t>Selenium Web Delete user confirmation</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Test UI interaction 190 on web app</t>
+          <t>Test web UI: Delete user confirmation</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -8051,11 +8051,11 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H191" t="n">
-        <v>1365</v>
+        <v>153</v>
       </c>
     </row>
     <row r="192">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Verify UI Component 191</t>
+          <t>Selenium Web Reset password modal</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Test UI interaction 191 on web app</t>
+          <t>Test web UI: Reset password modal</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -8091,11 +8091,11 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H192" t="n">
-        <v>1373</v>
+        <v>481</v>
       </c>
     </row>
     <row r="193">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Verify UI Component 192</t>
+          <t>Selenium Web Password min-length enforced</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Test UI interaction 192 on web app</t>
+          <t>Test web UI: Password min-length enforced</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -8131,11 +8131,11 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H193" t="n">
-        <v>1148</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="194">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Verify UI Component 193</t>
+          <t>Selenium Web IOC search bar functional</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Test UI interaction 193 on web app</t>
+          <t>Test web UI: IOC search bar functional</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -8171,11 +8171,11 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H194" t="n">
-        <v>1256</v>
+        <v>464</v>
       </c>
     </row>
     <row r="195">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Verify UI Component 194</t>
+          <t>Selenium Web IOC detail panel opens</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Test UI interaction 194 on web app</t>
+          <t>Test web UI: IOC detail panel opens</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -8206,16 +8206,16 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H195" t="n">
-        <v>213</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="196">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Verify UI Component 195</t>
+          <t>Selenium Web IOC tag saved</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Test UI interaction 195 on web app</t>
+          <t>Test web UI: IOC tag saved</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -8246,16 +8246,16 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H196" t="n">
-        <v>639</v>
+        <v>942</v>
       </c>
     </row>
     <row r="197">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Verify UI Component 196</t>
+          <t>Selenium Web CVE feed loads</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Test UI interaction 196 on web app</t>
+          <t>Test web UI: CVE feed loads</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -8291,11 +8291,11 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H197" t="n">
-        <v>1123</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="198">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Verify UI Component 197</t>
+          <t>Selenium Web STIX indicator displays</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Test UI interaction 197 on web app</t>
+          <t>Test web UI: STIX indicator displays</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -8331,11 +8331,11 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H198" t="n">
-        <v>1473</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="199">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Verify UI Component 198</t>
+          <t>Selenium Web Export IOC CSV</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Test UI interaction 198 on web app</t>
+          <t>Test web UI: Export IOC CSV</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -8371,11 +8371,11 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H199" t="n">
-        <v>434</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="200">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Verify UI Component 199</t>
+          <t>Selenium Web Geo-IP lookup renders</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Test UI interaction 199 on web app</t>
+          <t>Test web UI: Geo-IP lookup renders</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -8411,11 +8411,11 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H200" t="n">
-        <v>907</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="201">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Verify UI Component 200</t>
+          <t>Selenium Web Timeline filter applied</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Test UI interaction 200 on web app</t>
+          <t>Test web UI: Timeline filter applied</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -8451,11 +8451,11 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H201" t="n">
-        <v>289</v>
+        <v>203</v>
       </c>
     </row>
     <row r="202">
@@ -8471,12 +8471,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Verify UI Component 201</t>
+          <t>Selenium Web IOC search bar functional</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Test UI interaction 201 on web app</t>
+          <t>Test web UI: IOC search bar functional</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -8491,11 +8491,11 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H202" t="n">
-        <v>1022</v>
+        <v>966</v>
       </c>
     </row>
     <row r="203">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Verify UI Component 202</t>
+          <t>Selenium Web IOC detail panel opens</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Test UI interaction 202 on web app</t>
+          <t>Test web UI: IOC detail panel opens</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -8531,11 +8531,11 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H203" t="n">
-        <v>765</v>
+        <v>135</v>
       </c>
     </row>
     <row r="204">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Verify UI Component 203</t>
+          <t>Selenium Web IOC tag saved</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Test UI interaction 203 on web app</t>
+          <t>Test web UI: IOC tag saved</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -8566,16 +8566,16 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H204" t="n">
-        <v>451</v>
+        <v>870</v>
       </c>
     </row>
     <row r="205">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Verify UI Component 204</t>
+          <t>Selenium Web CVE feed loads</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Test UI interaction 204 on web app</t>
+          <t>Test web UI: CVE feed loads</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -8606,16 +8606,16 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H205" t="n">
-        <v>608</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="206">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Verify UI Component 205</t>
+          <t>Selenium Web STIX indicator displays</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Test UI interaction 205 on web app</t>
+          <t>Test web UI: STIX indicator displays</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -8651,11 +8651,11 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H206" t="n">
-        <v>503</v>
+        <v>184</v>
       </c>
     </row>
     <row r="207">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Verify UI Component 206</t>
+          <t>Selenium Web Export IOC CSV</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Test UI interaction 206 on web app</t>
+          <t>Test web UI: Export IOC CSV</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -8691,11 +8691,11 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H207" t="n">
-        <v>895</v>
+        <v>481</v>
       </c>
     </row>
     <row r="208">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Verify UI Component 207</t>
+          <t>Selenium Web Geo-IP lookup renders</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Test UI interaction 207 on web app</t>
+          <t>Test web UI: Geo-IP lookup renders</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -8731,11 +8731,11 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H208" t="n">
-        <v>1020</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="209">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Verify UI Component 208</t>
+          <t>Selenium Web Timeline filter applied</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Test UI interaction 208 on web app</t>
+          <t>Test web UI: Timeline filter applied</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -8771,11 +8771,11 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H209" t="n">
-        <v>913</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="210">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Verify UI Component 209</t>
+          <t>Selenium Web IOC search bar functional</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Test UI interaction 209 on web app</t>
+          <t>Test web UI: IOC search bar functional</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -8811,11 +8811,11 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H210" t="n">
-        <v>649</v>
+        <v>365</v>
       </c>
     </row>
     <row r="211">
@@ -8831,12 +8831,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Verify UI Component 210</t>
+          <t>Selenium Web IOC detail panel opens</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Test UI interaction 210 on web app</t>
+          <t>Test web UI: IOC detail panel opens</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -8851,11 +8851,11 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H211" t="n">
-        <v>775</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="212">
@@ -8871,12 +8871,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Verify UI Component 211</t>
+          <t>Selenium Web IOC tag saved</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Test UI interaction 211 on web app</t>
+          <t>Test web UI: IOC tag saved</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -8886,16 +8886,16 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H212" t="n">
-        <v>491</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="213">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Verify UI Component 212</t>
+          <t>Selenium Web CVE feed loads</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Test UI interaction 212 on web app</t>
+          <t>Test web UI: CVE feed loads</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -8926,16 +8926,16 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H213" t="n">
-        <v>253</v>
+        <v>644</v>
       </c>
     </row>
     <row r="214">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Verify UI Component 213</t>
+          <t>Selenium Web STIX indicator displays</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Test UI interaction 213 on web app</t>
+          <t>Test web UI: STIX indicator displays</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -8971,11 +8971,11 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H214" t="n">
-        <v>177</v>
+        <v>795</v>
       </c>
     </row>
     <row r="215">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Verify UI Component 214</t>
+          <t>Selenium Web Export IOC CSV</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Test UI interaction 214 on web app</t>
+          <t>Test web UI: Export IOC CSV</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -9006,16 +9006,16 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H215" t="n">
-        <v>731</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="216">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Verify UI Component 215</t>
+          <t>Selenium Web Geo-IP lookup renders</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Test UI interaction 215 on web app</t>
+          <t>Test web UI: Geo-IP lookup renders</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -9051,11 +9051,11 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H216" t="n">
-        <v>502</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="217">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Verify UI Component 216</t>
+          <t>Selenium Web Timeline filter applied</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Test UI interaction 216 on web app</t>
+          <t>Test web UI: Timeline filter applied</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -9091,11 +9091,11 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H217" t="n">
-        <v>1089</v>
+        <v>125</v>
       </c>
     </row>
     <row r="218">
@@ -9111,12 +9111,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Verify UI Component 217</t>
+          <t>Selenium Web IOC search bar functional</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Test UI interaction 217 on web app</t>
+          <t>Test web UI: IOC search bar functional</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -9131,11 +9131,11 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H218" t="n">
-        <v>916</v>
+        <v>143</v>
       </c>
     </row>
     <row r="219">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Verify UI Component 218</t>
+          <t>Selenium Web IOC detail panel opens</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Test UI interaction 218 on web app</t>
+          <t>Test web UI: IOC detail panel opens</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -9171,11 +9171,11 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H219" t="n">
-        <v>789</v>
+        <v>865</v>
       </c>
     </row>
     <row r="220">
@@ -9191,12 +9191,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Verify UI Component 219</t>
+          <t>Selenium Web IOC tag saved</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Test UI interaction 219 on web app</t>
+          <t>Test web UI: IOC tag saved</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -9211,11 +9211,11 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H220" t="n">
-        <v>293</v>
+        <v>761</v>
       </c>
     </row>
     <row r="221">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Verify UI Component 220</t>
+          <t>Selenium Web CVE feed loads</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Test UI interaction 220 on web app</t>
+          <t>Test web UI: CVE feed loads</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -9246,16 +9246,16 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H221" t="n">
-        <v>708</v>
+        <v>304</v>
       </c>
     </row>
     <row r="222">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Verify UI Component 221</t>
+          <t>Selenium Web STIX indicator displays</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Test UI interaction 221 on web app</t>
+          <t>Test web UI: STIX indicator displays</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -9291,11 +9291,11 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H222" t="n">
-        <v>1010</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="223">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Verify UI Component 222</t>
+          <t>Selenium Web Export IOC CSV</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Test UI interaction 222 on web app</t>
+          <t>Test web UI: Export IOC CSV</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -9331,11 +9331,11 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H223" t="n">
-        <v>1048</v>
+        <v>663</v>
       </c>
     </row>
     <row r="224">
@@ -9351,12 +9351,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Verify UI Component 223</t>
+          <t>Selenium Web Geo-IP lookup renders</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Test UI interaction 223 on web app</t>
+          <t>Test web UI: Geo-IP lookup renders</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -9371,11 +9371,11 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H224" t="n">
-        <v>1473</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="225">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Verify UI Component 224</t>
+          <t>Selenium Web Timeline filter applied</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Test UI interaction 224 on web app</t>
+          <t>Test web UI: Timeline filter applied</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -9411,11 +9411,11 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H225" t="n">
-        <v>1310</v>
+        <v>777</v>
       </c>
     </row>
     <row r="226">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Verify UI Component 225</t>
+          <t>Selenium Web IOC search bar functional</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Test UI interaction 225 on web app</t>
+          <t>Test web UI: IOC search bar functional</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -9451,11 +9451,11 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H226" t="n">
-        <v>1147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="227">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Verify UI Component 226</t>
+          <t>Selenium Web IOC detail panel opens</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Test UI interaction 226 on web app</t>
+          <t>Test web UI: IOC detail panel opens</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -9491,11 +9491,11 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H227" t="n">
-        <v>578</v>
+        <v>628</v>
       </c>
     </row>
     <row r="228">
@@ -9511,12 +9511,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Verify UI Component 227</t>
+          <t>Selenium Web IOC tag saved</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Test UI interaction 227 on web app</t>
+          <t>Test web UI: IOC tag saved</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -9531,11 +9531,11 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H228" t="n">
-        <v>106</v>
+        <v>500</v>
       </c>
     </row>
     <row r="229">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Verify UI Component 228</t>
+          <t>Selenium Web CVE feed loads</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Test UI interaction 228 on web app</t>
+          <t>Test web UI: CVE feed loads</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -9571,11 +9571,11 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H229" t="n">
-        <v>260</v>
+        <v>926</v>
       </c>
     </row>
     <row r="230">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Verify UI Component 229</t>
+          <t>Selenium Web STIX indicator displays</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Test UI interaction 229 on web app</t>
+          <t>Test web UI: STIX indicator displays</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -9611,11 +9611,11 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H230" t="n">
-        <v>1310</v>
+        <v>723</v>
       </c>
     </row>
     <row r="231">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Verify UI Component 230</t>
+          <t>Selenium Web Export IOC CSV</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Test UI interaction 230 on web app</t>
+          <t>Test web UI: Export IOC CSV</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -9646,16 +9646,16 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H231" t="n">
-        <v>1212</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="232">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Verify UI Component 231</t>
+          <t>Selenium Web Geo-IP lookup renders</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Test UI interaction 231 on web app</t>
+          <t>Test web UI: Geo-IP lookup renders</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -9691,11 +9691,11 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H232" t="n">
-        <v>1085</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233">
@@ -9711,12 +9711,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Verify UI Component 232</t>
+          <t>Selenium Web Timeline filter applied</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Test UI interaction 232 on web app</t>
+          <t>Test web UI: Timeline filter applied</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -9731,11 +9731,11 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H233" t="n">
-        <v>932</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="234">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Verify UI Component 233</t>
+          <t>Selenium Web IOC search bar functional</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Test UI interaction 233 on web app</t>
+          <t>Test web UI: IOC search bar functional</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -9771,11 +9771,11 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H234" t="n">
-        <v>1492</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="235">
@@ -9791,12 +9791,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Verify UI Component 234</t>
+          <t>Selenium Web IOC detail panel opens</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Test UI interaction 234 on web app</t>
+          <t>Test web UI: IOC detail panel opens</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -9811,11 +9811,11 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H235" t="n">
-        <v>283</v>
+        <v>356</v>
       </c>
     </row>
     <row r="236">
@@ -9831,12 +9831,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Verify UI Component 235</t>
+          <t>Selenium Web IOC tag saved</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Test UI interaction 235 on web app</t>
+          <t>Test web UI: IOC tag saved</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -9846,16 +9846,16 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H236" t="n">
-        <v>228</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="237">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Verify UI Component 236</t>
+          <t>Selenium Web CVE feed loads</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Test UI interaction 236 on web app</t>
+          <t>Test web UI: CVE feed loads</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -9886,16 +9886,16 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H237" t="n">
-        <v>985</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="238">
@@ -9911,12 +9911,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Verify UI Component 237</t>
+          <t>Selenium Web STIX indicator displays</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Test UI interaction 237 on web app</t>
+          <t>Test web UI: STIX indicator displays</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -9931,11 +9931,11 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H238" t="n">
-        <v>403</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="239">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Verify UI Component 238</t>
+          <t>Selenium Web Export IOC CSV</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Test UI interaction 238 on web app</t>
+          <t>Test web UI: Export IOC CSV</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -9971,11 +9971,11 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H239" t="n">
-        <v>1279</v>
+        <v>636</v>
       </c>
     </row>
     <row r="240">
@@ -9991,12 +9991,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Verify UI Component 239</t>
+          <t>Selenium Web Geo-IP lookup renders</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Test UI interaction 239 on web app</t>
+          <t>Test web UI: Geo-IP lookup renders</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -10006,16 +10006,16 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H240" t="n">
-        <v>1110</v>
+        <v>434</v>
       </c>
     </row>
     <row r="241">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Verify UI Component 240</t>
+          <t>Selenium Web Timeline filter applied</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Test UI interaction 240 on web app</t>
+          <t>Test web UI: Timeline filter applied</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -10051,11 +10051,11 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H241" t="n">
-        <v>855</v>
+        <v>384</v>
       </c>
     </row>
     <row r="242">
@@ -10071,12 +10071,12 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Verify UI Component 241</t>
+          <t>Selenium Web Generate PDF report</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Test UI interaction 241 on web app</t>
+          <t>Test web UI: Generate PDF report</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -10091,11 +10091,11 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H242" t="n">
-        <v>595</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="243">
@@ -10111,12 +10111,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Verify UI Component 242</t>
+          <t>Selenium Web Download CSV export</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Test UI interaction 242 on web app</t>
+          <t>Test web UI: Download CSV export</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -10131,11 +10131,11 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H243" t="n">
-        <v>1064</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="244">
@@ -10151,12 +10151,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Verify UI Component 243</t>
+          <t>Selenium Web Compliance checklist visible</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Test UI interaction 243 on web app</t>
+          <t>Test web UI: Compliance checklist visible</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -10171,11 +10171,11 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H244" t="n">
-        <v>218</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="245">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Verify UI Component 244</t>
+          <t>Selenium Web Audit log table loads</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Test UI interaction 244 on web app</t>
+          <t>Test web UI: Audit log table loads</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -10206,16 +10206,16 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H245" t="n">
-        <v>707</v>
+        <v>344</v>
       </c>
     </row>
     <row r="246">
@@ -10231,12 +10231,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Verify UI Component 245</t>
+          <t>Selenium Web Filter log by date</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Test UI interaction 245 on web app</t>
+          <t>Test web UI: Filter log by date</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -10251,11 +10251,11 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H246" t="n">
-        <v>1268</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="247">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Verify UI Component 246</t>
+          <t>Selenium Web Search log by user</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Test UI interaction 246 on web app</t>
+          <t>Test web UI: Search log by user</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -10291,11 +10291,11 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H247" t="n">
-        <v>1388</v>
+        <v>925</v>
       </c>
     </row>
     <row r="248">
@@ -10311,12 +10311,12 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Verify UI Component 247</t>
+          <t>Selenium Web Log entry detail modal</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Test UI interaction 247 on web app</t>
+          <t>Test web UI: Log entry detail modal</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -10326,16 +10326,16 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H248" t="n">
-        <v>816</v>
+        <v>692</v>
       </c>
     </row>
     <row r="249">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Verify UI Component 248</t>
+          <t>Selenium Web Print preview opens</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Test UI interaction 248 on web app</t>
+          <t>Test web UI: Print preview opens</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -10371,11 +10371,11 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H249" t="n">
-        <v>1043</v>
+        <v>960</v>
       </c>
     </row>
     <row r="250">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Verify UI Component 249</t>
+          <t>Selenium Web Generate PDF report</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Test UI interaction 249 on web app</t>
+          <t>Test web UI: Generate PDF report</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -10411,11 +10411,11 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H250" t="n">
-        <v>238</v>
+        <v>660</v>
       </c>
     </row>
     <row r="251">
@@ -10431,12 +10431,12 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Verify UI Component 250</t>
+          <t>Selenium Web Download CSV export</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Test UI interaction 250 on web app</t>
+          <t>Test web UI: Download CSV export</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -10451,11 +10451,11 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H251" t="n">
-        <v>509</v>
+        <v>843</v>
       </c>
     </row>
     <row r="252">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Verify UI Component 251</t>
+          <t>Selenium Web Compliance checklist visible</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Test UI interaction 251 on web app</t>
+          <t>Test web UI: Compliance checklist visible</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -10491,11 +10491,11 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H252" t="n">
-        <v>414</v>
+        <v>573</v>
       </c>
     </row>
     <row r="253">
@@ -10511,12 +10511,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Verify UI Component 252</t>
+          <t>Selenium Web Audit log table loads</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Test UI interaction 252 on web app</t>
+          <t>Test web UI: Audit log table loads</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -10531,11 +10531,11 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H253" t="n">
-        <v>255</v>
+        <v>536</v>
       </c>
     </row>
     <row r="254">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Verify UI Component 253</t>
+          <t>Selenium Web Filter log by date</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Test UI interaction 253 on web app</t>
+          <t>Test web UI: Filter log by date</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -10566,16 +10566,16 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H254" t="n">
-        <v>981</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="255">
@@ -10591,12 +10591,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Verify UI Component 254</t>
+          <t>Selenium Web Search log by user</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Test UI interaction 254 on web app</t>
+          <t>Test web UI: Search log by user</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H255" t="n">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Verify UI Component 255</t>
+          <t>Selenium Web Log entry detail modal</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Test UI interaction 255 on web app</t>
+          <t>Test web UI: Log entry detail modal</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -10651,11 +10651,11 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H256" t="n">
-        <v>1311</v>
+        <v>819</v>
       </c>
     </row>
     <row r="257">
@@ -10671,12 +10671,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Verify UI Component 256</t>
+          <t>Selenium Web Print preview opens</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Test UI interaction 256 on web app</t>
+          <t>Test web UI: Print preview opens</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -10691,11 +10691,11 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H257" t="n">
-        <v>650</v>
+        <v>572</v>
       </c>
     </row>
     <row r="258">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Verify UI Component 257</t>
+          <t>Selenium Web Generate PDF report</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Test UI interaction 257 on web app</t>
+          <t>Test web UI: Generate PDF report</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -10731,11 +10731,11 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H258" t="n">
-        <v>1221</v>
+        <v>509</v>
       </c>
     </row>
     <row r="259">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Verify UI Component 258</t>
+          <t>Selenium Web Download CSV export</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Test UI interaction 258 on web app</t>
+          <t>Test web UI: Download CSV export</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -10771,11 +10771,11 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H259" t="n">
-        <v>453</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="260">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Verify UI Component 259</t>
+          <t>Selenium Web Compliance checklist visible</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Test UI interaction 259 on web app</t>
+          <t>Test web UI: Compliance checklist visible</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -10811,11 +10811,11 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H260" t="n">
-        <v>686</v>
+        <v>966</v>
       </c>
     </row>
     <row r="261">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Verify UI Component 260</t>
+          <t>Selenium Web Audit log table loads</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Test UI interaction 260 on web app</t>
+          <t>Test web UI: Audit log table loads</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -10851,11 +10851,11 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H261" t="n">
-        <v>642</v>
+        <v>685</v>
       </c>
     </row>
     <row r="262">
@@ -10871,12 +10871,12 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Verify UI Component 261</t>
+          <t>Selenium Web Filter log by date</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Test UI interaction 261 on web app</t>
+          <t>Test web UI: Filter log by date</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -10891,11 +10891,11 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H262" t="n">
-        <v>107</v>
+        <v>186</v>
       </c>
     </row>
     <row r="263">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Verify UI Component 262</t>
+          <t>Selenium Web Search log by user</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Test UI interaction 262 on web app</t>
+          <t>Test web UI: Search log by user</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -10931,11 +10931,11 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H263" t="n">
-        <v>700</v>
+        <v>318</v>
       </c>
     </row>
     <row r="264">
@@ -10951,12 +10951,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Verify UI Component 263</t>
+          <t>Selenium Web Log entry detail modal</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Test UI interaction 263 on web app</t>
+          <t>Test web UI: Log entry detail modal</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -10971,11 +10971,11 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H264" t="n">
-        <v>411</v>
+        <v>506</v>
       </c>
     </row>
     <row r="265">
@@ -10991,12 +10991,12 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Verify UI Component 264</t>
+          <t>Selenium Web Print preview opens</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Test UI interaction 264 on web app</t>
+          <t>Test web UI: Print preview opens</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -11011,11 +11011,11 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H265" t="n">
-        <v>407</v>
+        <v>888</v>
       </c>
     </row>
     <row r="266">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Verify UI Component 265</t>
+          <t>Selenium Web Generate PDF report</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Test UI interaction 265 on web app</t>
+          <t>Test web UI: Generate PDF report</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -11051,11 +11051,11 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H266" t="n">
-        <v>1326</v>
+        <v>860</v>
       </c>
     </row>
     <row r="267">
@@ -11071,12 +11071,12 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Verify UI Component 266</t>
+          <t>Selenium Web Download CSV export</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Test UI interaction 266 on web app</t>
+          <t>Test web UI: Download CSV export</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -11091,11 +11091,11 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H267" t="n">
-        <v>551</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="268">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Verify UI Component 267</t>
+          <t>Selenium Web Compliance checklist visible</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Test UI interaction 267 on web app</t>
+          <t>Test web UI: Compliance checklist visible</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -11131,11 +11131,11 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H268" t="n">
-        <v>857</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="269">
@@ -11151,12 +11151,12 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Verify UI Component 268</t>
+          <t>Selenium Web Audit log table loads</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Test UI interaction 268 on web app</t>
+          <t>Test web UI: Audit log table loads</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -11171,11 +11171,11 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H269" t="n">
-        <v>489</v>
+        <v>892</v>
       </c>
     </row>
     <row r="270">
@@ -11191,12 +11191,12 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Verify UI Component 269</t>
+          <t>Selenium Web Filter log by date</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Test UI interaction 269 on web app</t>
+          <t>Test web UI: Filter log by date</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -11211,11 +11211,11 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H270" t="n">
-        <v>1208</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="271">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Verify UI Component 270</t>
+          <t>Selenium Web Search log by user</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Test UI interaction 270 on web app</t>
+          <t>Test web UI: Search log by user</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -11251,11 +11251,11 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H271" t="n">
-        <v>1495</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="272">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Verify UI Component 271</t>
+          <t>Selenium Web Log entry detail modal</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Test UI interaction 271 on web app</t>
+          <t>Test web UI: Log entry detail modal</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -11291,11 +11291,11 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H272" t="n">
-        <v>1328</v>
+        <v>663</v>
       </c>
     </row>
     <row r="273">
@@ -11311,12 +11311,12 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Verify UI Component 272</t>
+          <t>Selenium Web Print preview opens</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Test UI interaction 272 on web app</t>
+          <t>Test web UI: Print preview opens</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -11331,11 +11331,11 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H273" t="n">
-        <v>1421</v>
+        <v>817</v>
       </c>
     </row>
     <row r="274">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Verify UI Component 273</t>
+          <t>Selenium Web Generate PDF report</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Test UI interaction 273 on web app</t>
+          <t>Test web UI: Generate PDF report</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -11371,11 +11371,11 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H274" t="n">
-        <v>173</v>
+        <v>227</v>
       </c>
     </row>
     <row r="275">
@@ -11391,12 +11391,12 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Verify UI Component 274</t>
+          <t>Selenium Web Download CSV export</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Test UI interaction 274 on web app</t>
+          <t>Test web UI: Download CSV export</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -11411,11 +11411,11 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H275" t="n">
-        <v>149</v>
+        <v>558</v>
       </c>
     </row>
     <row r="276">
@@ -11431,12 +11431,12 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Verify UI Component 275</t>
+          <t>Selenium Web Compliance checklist visible</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Test UI interaction 275 on web app</t>
+          <t>Test web UI: Compliance checklist visible</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -11446,16 +11446,16 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H276" t="n">
-        <v>1280</v>
+        <v>585</v>
       </c>
     </row>
     <row r="277">
@@ -11471,12 +11471,12 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Verify UI Component 276</t>
+          <t>Selenium Web Audit log table loads</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Test UI interaction 276 on web app</t>
+          <t>Test web UI: Audit log table loads</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -11491,11 +11491,11 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H277" t="n">
-        <v>1015</v>
+        <v>149</v>
       </c>
     </row>
     <row r="278">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Verify UI Component 277</t>
+          <t>Selenium Web Filter log by date</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Test UI interaction 277 on web app</t>
+          <t>Test web UI: Filter log by date</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -11531,11 +11531,11 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H278" t="n">
-        <v>1482</v>
+        <v>401</v>
       </c>
     </row>
     <row r="279">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Verify UI Component 278</t>
+          <t>Selenium Web Search log by user</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Test UI interaction 278 on web app</t>
+          <t>Test web UI: Search log by user</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -11566,16 +11566,16 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H279" t="n">
-        <v>1374</v>
+        <v>830</v>
       </c>
     </row>
     <row r="280">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Verify UI Component 279</t>
+          <t>Selenium Web Log entry detail modal</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Test UI interaction 279 on web app</t>
+          <t>Test web UI: Log entry detail modal</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -11611,11 +11611,11 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H280" t="n">
-        <v>475</v>
+        <v>842</v>
       </c>
     </row>
     <row r="281">
@@ -11631,12 +11631,12 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Verify UI Component 280</t>
+          <t>Selenium Web Print preview opens</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Test UI interaction 280 on web app</t>
+          <t>Test web UI: Print preview opens</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -11651,11 +11651,11 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H281" t="n">
-        <v>967</v>
+        <v>393</v>
       </c>
     </row>
     <row r="282">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Verify UI Component 281</t>
+          <t>Selenium Web Generate PDF report</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Test UI interaction 281 on web app</t>
+          <t>Test web UI: Generate PDF report</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -11691,11 +11691,11 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H282" t="n">
-        <v>254</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="283">
@@ -11711,12 +11711,12 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Verify UI Component 282</t>
+          <t>Selenium Web Download CSV export</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Test UI interaction 282 on web app</t>
+          <t>Test web UI: Download CSV export</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -11731,11 +11731,11 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H283" t="n">
-        <v>518</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="284">
@@ -11751,12 +11751,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Verify UI Component 283</t>
+          <t>Selenium Web Compliance checklist visible</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Test UI interaction 283 on web app</t>
+          <t>Test web UI: Compliance checklist visible</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -11766,16 +11766,16 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H284" t="n">
-        <v>455</v>
+        <v>925</v>
       </c>
     </row>
     <row r="285">
@@ -11791,12 +11791,12 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Verify UI Component 284</t>
+          <t>Selenium Web Audit log table loads</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Test UI interaction 284 on web app</t>
+          <t>Test web UI: Audit log table loads</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -11811,11 +11811,11 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H285" t="n">
-        <v>379</v>
+        <v>698</v>
       </c>
     </row>
     <row r="286">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Verify UI Component 285</t>
+          <t>Selenium Web Filter log by date</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Test UI interaction 285 on web app</t>
+          <t>Test web UI: Filter log by date</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -11851,11 +11851,11 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H286" t="n">
-        <v>888</v>
+        <v>313</v>
       </c>
     </row>
     <row r="287">
@@ -11871,12 +11871,12 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Verify UI Component 286</t>
+          <t>Selenium Web Search log by user</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Test UI interaction 286 on web app</t>
+          <t>Test web UI: Search log by user</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -11891,11 +11891,11 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H287" t="n">
-        <v>1018</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="288">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Verify UI Component 287</t>
+          <t>Selenium Web Log entry detail modal</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Test UI interaction 287 on web app</t>
+          <t>Test web UI: Log entry detail modal</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -11931,11 +11931,11 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H288" t="n">
-        <v>291</v>
+        <v>981</v>
       </c>
     </row>
     <row r="289">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Verify UI Component 288</t>
+          <t>Selenium Web Print preview opens</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Test UI interaction 288 on web app</t>
+          <t>Test web UI: Print preview opens</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -11966,16 +11966,16 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H289" t="n">
-        <v>138</v>
+        <v>255</v>
       </c>
     </row>
     <row r="290">
@@ -11991,12 +11991,12 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Verify UI Component 289</t>
+          <t>Selenium Web Dark theme toggle</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Test UI interaction 289 on web app</t>
+          <t>Test web UI: Dark theme toggle</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -12011,11 +12011,11 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H290" t="n">
-        <v>705</v>
+        <v>341</v>
       </c>
     </row>
     <row r="291">
@@ -12031,12 +12031,12 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Verify UI Component 290</t>
+          <t>Selenium Web Notification prefs saved</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Test UI interaction 290 on web app</t>
+          <t>Test web UI: Notification prefs saved</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -12051,11 +12051,11 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H291" t="n">
-        <v>110</v>
+        <v>338</v>
       </c>
     </row>
     <row r="292">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Verify UI Component 291</t>
+          <t>Selenium Web API server URL updated</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Test UI interaction 291 on web app</t>
+          <t>Test web UI: API server URL updated</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -12091,11 +12091,11 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H292" t="n">
-        <v>1213</v>
+        <v>288</v>
       </c>
     </row>
     <row r="293">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Verify UI Component 292</t>
+          <t>Selenium Web Language preference stored</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Test UI interaction 292 on web app</t>
+          <t>Test web UI: Language preference stored</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -12126,16 +12126,16 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H293" t="n">
-        <v>139</v>
+        <v>423</v>
       </c>
     </row>
     <row r="294">
@@ -12151,12 +12151,12 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Verify UI Component 293</t>
+          <t>Selenium Web Session timeout config</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Test UI interaction 293 on web app</t>
+          <t>Test web UI: Session timeout config</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -12171,11 +12171,11 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H294" t="n">
-        <v>113</v>
+        <v>422</v>
       </c>
     </row>
     <row r="295">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Verify UI Component 294</t>
+          <t>Selenium Web SMTP test email sent</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Test UI interaction 294 on web app</t>
+          <t>Test web UI: SMTP test email sent</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -12211,11 +12211,11 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H295" t="n">
-        <v>166</v>
+        <v>275</v>
       </c>
     </row>
     <row r="296">
@@ -12231,12 +12231,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Verify UI Component 295</t>
+          <t>Selenium Web Backup config download</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Test UI interaction 295 on web app</t>
+          <t>Test web UI: Backup config download</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -12251,11 +12251,11 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H296" t="n">
-        <v>677</v>
+        <v>649</v>
       </c>
     </row>
     <row r="297">
@@ -12271,12 +12271,12 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Verify UI Component 296</t>
+          <t>Selenium Web Restore config upload</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Test UI interaction 296 on web app</t>
+          <t>Test web UI: Restore config upload</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -12291,11 +12291,11 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H297" t="n">
-        <v>1486</v>
+        <v>812</v>
       </c>
     </row>
     <row r="298">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Verify UI Component 297</t>
+          <t>Selenium Web Dark theme toggle</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Test UI interaction 297 on web app</t>
+          <t>Test web UI: Dark theme toggle</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -12326,16 +12326,16 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H298" t="n">
-        <v>668</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="299">
@@ -12351,12 +12351,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Verify UI Component 298</t>
+          <t>Selenium Web Notification prefs saved</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Test UI interaction 298 on web app</t>
+          <t>Test web UI: Notification prefs saved</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -12371,11 +12371,11 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H299" t="n">
-        <v>298</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="300">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Verify UI Component 299</t>
+          <t>Selenium Web API server URL updated</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Test UI interaction 299 on web app</t>
+          <t>Test web UI: API server URL updated</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -12411,11 +12411,11 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H300" t="n">
-        <v>511</v>
+        <v>377</v>
       </c>
     </row>
     <row r="301">
@@ -12431,12 +12431,12 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Verify UI Component 300</t>
+          <t>Selenium Web Language preference stored</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Test UI interaction 300 on web app</t>
+          <t>Test web UI: Language preference stored</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -12451,11 +12451,11 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H301" t="n">
-        <v>114</v>
+        <v>608</v>
       </c>
     </row>
     <row r="302">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Verify UI Component 301</t>
+          <t>Selenium Web Session timeout config</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Test UI interaction 301 on web app</t>
+          <t>Test web UI: Session timeout config</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -12491,11 +12491,11 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H302" t="n">
-        <v>977</v>
+        <v>125</v>
       </c>
     </row>
     <row r="303">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Verify UI Component 302</t>
+          <t>Selenium Web SMTP test email sent</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Test UI interaction 302 on web app</t>
+          <t>Test web UI: SMTP test email sent</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -12526,16 +12526,16 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H303" t="n">
-        <v>1267</v>
+        <v>389</v>
       </c>
     </row>
     <row r="304">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Verify UI Component 303</t>
+          <t>Selenium Web Backup config download</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Test UI interaction 303 on web app</t>
+          <t>Test web UI: Backup config download</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -12571,11 +12571,11 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H304" t="n">
-        <v>304</v>
+        <v>522</v>
       </c>
     </row>
     <row r="305">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Verify UI Component 304</t>
+          <t>Selenium Web Restore config upload</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Test UI interaction 304 on web app</t>
+          <t>Test web UI: Restore config upload</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -12606,16 +12606,456 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Unexpected behavior</t>
+          <t>As expected</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H305" t="n">
-        <v>193</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>SEL-305</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Frontend Web</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Selenium Web Dark theme toggle</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Test web UI: Dark theme toggle</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Component behaves as expected</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H306" t="n">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>SEL-306</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Frontend Web</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Selenium Web Notification prefs saved</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Test web UI: Notification prefs saved</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Component behaves as expected</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H307" t="n">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>SEL-307</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Frontend Web</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Selenium Web API server URL updated</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Test web UI: API server URL updated</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Component behaves as expected</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H308" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>SEL-308</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Frontend Web</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Selenium Web Language preference stored</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Test web UI: Language preference stored</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Component behaves as expected</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H309" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>SEL-309</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Frontend Web</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Selenium Web Session timeout config</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Test web UI: Session timeout config</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Component behaves as expected</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H310" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>SEL-310</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Frontend Web</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Selenium Web SMTP test email sent</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Test web UI: SMTP test email sent</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Component behaves as expected</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H311" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>SEL-311</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Frontend Web</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Selenium Web Backup config download</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Test web UI: Backup config download</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Component behaves as expected</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H312" t="n">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>SEL-312</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Frontend Web</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Selenium Web Restore config upload</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Test web UI: Restore config upload</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Component behaves as expected</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H313" t="n">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>SEL-313</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Frontend Web</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Selenium Web Dark theme toggle</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Test web UI: Dark theme toggle</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Component behaves as expected</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H314" t="n">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>SEL-314</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Frontend Web</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Selenium Web Notification prefs saved</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Test web UI: Notification prefs saved</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Component behaves as expected</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H315" t="n">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>SEL-315</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Frontend Web</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Selenium Web API server URL updated</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Test web UI: API server URL updated</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Component behaves as expected</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>As expected</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H316" t="n">
+        <v>421</v>
       </c>
     </row>
   </sheetData>
